--- a/data/trans_orig/P16A07-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A07-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30083</t>
+          <t>29067</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55952</t>
+          <t>55338</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>109252</t>
+          <t>109256</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>153103</t>
+          <t>152335</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>146762</t>
+          <t>145453</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199114</t>
+          <t>196606</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>975771</t>
+          <t>976385</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1001640</t>
+          <t>1002656</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1162010</t>
+          <t>1162778</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1205861</t>
+          <t>1205857</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2147721</t>
+          <t>2150229</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2200073</t>
+          <t>2201382</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10421</t>
+          <t>10852</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27527</t>
+          <t>27334</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56197</t>
+          <t>55993</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90363</t>
+          <t>88193</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73440</t>
+          <t>72168</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112165</t>
+          <t>109540</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1664867</t>
+          <t>1665060</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1681973</t>
+          <t>1681542</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1497310</t>
+          <t>1499480</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1531476</t>
+          <t>1531680</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3167902</t>
+          <t>3170527</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3206627</t>
+          <t>3207899</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19212</t>
+          <t>20080</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26403</t>
+          <t>26657</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19682</t>
+          <t>19805</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40407</t>
+          <t>42239</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>532196</t>
+          <t>531328</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545619</t>
+          <t>545495</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>450009</t>
+          <t>449755</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>466615</t>
+          <t>465698</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>987413</t>
+          <t>985581</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1008138</t>
+          <t>1008015</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55089</t>
+          <t>55132</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85755</t>
+          <t>88484</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>190280</t>
+          <t>190996</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>246748</t>
+          <t>247695</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>255230</t>
+          <t>259067</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>320257</t>
+          <t>319516</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3189770</t>
+          <t>3187041</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3220436</t>
+          <t>3220393</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3132449</t>
+          <t>3131502</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3188917</t>
+          <t>3188201</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6334465</t>
+          <t>6335206</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6399492</t>
+          <t>6395655</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35685</t>
+          <t>36546</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66230</t>
+          <t>66248</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>165006</t>
+          <t>164313</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>216579</t>
+          <t>216833</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>213100</t>
+          <t>212995</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>273013</t>
+          <t>270172</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>905607</t>
+          <t>905589</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>936152</t>
+          <t>935291</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1115868</t>
+          <t>1115614</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1167441</t>
+          <t>1168134</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2031271</t>
+          <t>2034112</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2091184</t>
+          <t>2091289</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,76%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33662</t>
+          <t>34681</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63840</t>
+          <t>63481</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>78494</t>
+          <t>78858</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>119733</t>
+          <t>119679</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>118599</t>
+          <t>122651</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>169282</t>
+          <t>173147</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1895141</t>
+          <t>1895500</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1925319</t>
+          <t>1924300</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1632902</t>
+          <t>1632956</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1674141</t>
+          <t>1673777</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3542333</t>
+          <t>3538468</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3593016</t>
+          <t>3588964</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19207</t>
+          <t>19058</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17527</t>
+          <t>18247</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10049</t>
+          <t>11073</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31151</t>
+          <t>30063</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>461125</t>
+          <t>461274</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>476472</t>
+          <t>477116</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>440127</t>
+          <t>439407</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>452898</t>
+          <t>453079</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>906835</t>
+          <t>907923</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>927937</t>
+          <t>926913</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84587</t>
+          <t>86017</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127464</t>
+          <t>133067</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>261124</t>
+          <t>264389</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>327167</t>
+          <t>335130</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>363046</t>
+          <t>363556</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>441640</t>
+          <t>446581</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3283686</t>
+          <t>3278083</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3326563</t>
+          <t>3325133</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3215569</t>
+          <t>3207606</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3281612</t>
+          <t>3278347</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6512246</t>
+          <t>6507305</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6590840</t>
+          <t>6590330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21620</t>
+          <t>21043</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44154</t>
+          <t>44190</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93670</t>
+          <t>93234</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>135694</t>
+          <t>134735</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>121311</t>
+          <t>121978</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>167894</t>
+          <t>168122</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>710193</t>
+          <t>710157</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>732727</t>
+          <t>733304</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>858966</t>
+          <t>859925</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>900990</t>
+          <t>901426</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1581113</t>
+          <t>1580885</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1627696</t>
+          <t>1627029</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,03%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28878</t>
+          <t>28384</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53630</t>
+          <t>53751</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>102619</t>
+          <t>99200</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145512</t>
+          <t>145772</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>136367</t>
+          <t>137227</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>188046</t>
+          <t>189645</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2022755</t>
+          <t>2022634</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2047507</t>
+          <t>2048001</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1842788</t>
+          <t>1842528</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1885681</t>
+          <t>1889100</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3876639</t>
+          <t>3875040</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3928318</t>
+          <t>3927458</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8501</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25355</t>
+          <t>25362</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>10132</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28586</t>
+          <t>28578</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>538205</t>
+          <t>538905</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>523785</t>
+          <t>523778</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>540639</t>
+          <t>541140</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1067441</t>
+          <t>1067449</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1086186</t>
+          <t>1085895</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58053</t>
+          <t>57906</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92805</t>
+          <t>94451</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>218891</t>
+          <t>218483</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>284486</t>
+          <t>279133</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>287392</t>
+          <t>287840</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>360065</t>
+          <t>360314</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3284813</t>
+          <t>3283167</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3319565</t>
+          <t>3319712</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3247614</t>
+          <t>3252967</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3313209</t>
+          <t>3313617</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6549653</t>
+          <t>6549404</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6622326</t>
+          <t>6621878</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24961</t>
+          <t>25614</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45634</t>
+          <t>46955</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>84281</t>
+          <t>85499</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110900</t>
+          <t>112940</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>116077</t>
+          <t>116605</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>149973</t>
+          <t>151063</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>467818</t>
+          <t>466497</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>488491</t>
+          <t>487838</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>640832</t>
+          <t>638792</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>667451</t>
+          <t>666233</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1115210</t>
+          <t>1114120</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1149106</t>
+          <t>1148578</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,78%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43380</t>
+          <t>43075</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82476</t>
+          <t>83020</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>100199</t>
+          <t>100360</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>164560</t>
+          <t>166108</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>164390</t>
+          <t>160003</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>236903</t>
+          <t>234707</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2207851</t>
+          <t>2207307</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2246947</t>
+          <t>2247252</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2072585</t>
+          <t>2071037</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2136946</t>
+          <t>2136785</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4290569</t>
+          <t>4292765</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4363082</t>
+          <t>4367469</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8115</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24686</t>
+          <t>24174</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18006</t>
+          <t>18220</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35047</t>
+          <t>35232</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29784</t>
+          <t>28641</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51882</t>
+          <t>51680</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>621937</t>
+          <t>622449</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>638508</t>
+          <t>638700</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>625416</t>
+          <t>625231</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>642457</t>
+          <t>642243</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1255204</t>
+          <t>1255406</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1277302</t>
+          <t>1278445</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85743</t>
+          <t>84603</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>136191</t>
+          <t>135418</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>217257</t>
+          <t>212173</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>292827</t>
+          <t>292825</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>324786</t>
+          <t>323657</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>411496</t>
+          <t>412193</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3314211</t>
+          <t>3314984</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3364659</t>
+          <t>3365799</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3356512</t>
+          <t>3356514</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3432082</t>
+          <t>3437166</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6688246</t>
+          <t>6687549</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6774956</t>
+          <t>6776085</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A07-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A07-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29067</t>
+          <t>30249</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55338</t>
+          <t>55241</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>109256</t>
+          <t>109014</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>152335</t>
+          <t>155845</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>145453</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>196606</t>
+          <t>198921</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>976385</t>
+          <t>976482</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1002656</t>
+          <t>1001474</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1162778</t>
+          <t>1159268</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1205857</t>
+          <t>1206099</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2150229</t>
+          <t>2147914</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2201382</t>
+          <t>2201580</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10852</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27334</t>
+          <t>26893</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55993</t>
+          <t>56090</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>88193</t>
+          <t>89923</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72168</t>
+          <t>72638</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109540</t>
+          <t>108568</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1665060</t>
+          <t>1665501</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1681542</t>
+          <t>1681636</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1499480</t>
+          <t>1497750</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1531680</t>
+          <t>1531583</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3170527</t>
+          <t>3171499</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3207899</t>
+          <t>3207429</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>17943</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26657</t>
+          <t>26796</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19805</t>
+          <t>19289</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42239</t>
+          <t>40176</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>531328</t>
+          <t>533465</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545495</t>
+          <t>545712</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>449755</t>
+          <t>449616</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>465698</t>
+          <t>466507</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>985581</t>
+          <t>987644</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1008015</t>
+          <t>1008531</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55132</t>
+          <t>54910</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88484</t>
+          <t>87621</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>190996</t>
+          <t>190667</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>247695</t>
+          <t>247809</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>259067</t>
+          <t>256746</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>319516</t>
+          <t>323336</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3187041</t>
+          <t>3187904</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3220393</t>
+          <t>3220615</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3131502</t>
+          <t>3131388</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3188201</t>
+          <t>3188530</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6335206</t>
+          <t>6331386</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6395655</t>
+          <t>6397976</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36546</t>
+          <t>37280</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66248</t>
+          <t>67037</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>164313</t>
+          <t>167225</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>216833</t>
+          <t>220482</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>212995</t>
+          <t>212969</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>270172</t>
+          <t>274997</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>905589</t>
+          <t>904800</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>935291</t>
+          <t>934557</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1115614</t>
+          <t>1111965</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1168134</t>
+          <t>1165222</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2034112</t>
+          <t>2029287</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2091289</t>
+          <t>2091315</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34681</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63481</t>
+          <t>63303</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>78858</t>
+          <t>78608</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>119679</t>
+          <t>118767</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>122651</t>
+          <t>121125</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>173147</t>
+          <t>170677</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1895500</t>
+          <t>1895678</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1924300</t>
+          <t>1924352</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1632956</t>
+          <t>1633868</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1673777</t>
+          <t>1674027</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3538468</t>
+          <t>3540938</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3588964</t>
+          <t>3590490</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19058</t>
+          <t>19414</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18247</t>
+          <t>17710</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30063</t>
+          <t>31696</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>461274</t>
+          <t>460918</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>477116</t>
+          <t>477143</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>439407</t>
+          <t>439944</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>453079</t>
+          <t>452871</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>907923</t>
+          <t>906290</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>926913</t>
+          <t>927057</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86017</t>
+          <t>86761</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133067</t>
+          <t>132115</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>264389</t>
+          <t>264632</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>335130</t>
+          <t>332118</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>363556</t>
+          <t>366947</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>446581</t>
+          <t>449457</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3278083</t>
+          <t>3279035</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3325133</t>
+          <t>3324389</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3207606</t>
+          <t>3210618</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3278347</t>
+          <t>3278104</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6507305</t>
+          <t>6504429</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6590330</t>
+          <t>6586939</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,72%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21043</t>
+          <t>22419</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44190</t>
+          <t>45517</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93234</t>
+          <t>93022</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134735</t>
+          <t>133587</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>121978</t>
+          <t>121320</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>168122</t>
+          <t>167452</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>710157</t>
+          <t>708830</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>733304</t>
+          <t>731928</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>859925</t>
+          <t>861073</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>901426</t>
+          <t>901638</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1580885</t>
+          <t>1581555</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1627029</t>
+          <t>1627687</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,06%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28384</t>
+          <t>28070</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53751</t>
+          <t>53689</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>99200</t>
+          <t>102191</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145772</t>
+          <t>146328</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>137227</t>
+          <t>137166</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>189645</t>
+          <t>190839</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2022634</t>
+          <t>2022696</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2048001</t>
+          <t>2048315</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1842528</t>
+          <t>1841972</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1889100</t>
+          <t>1886109</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3875040</t>
+          <t>3873846</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3927458</t>
+          <t>3927519</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>882</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25362</t>
+          <t>24343</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10132</t>
+          <t>10620</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28578</t>
+          <t>29388</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>538905</t>
+          <t>538753</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>546001</t>
+          <t>546004</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>523778</t>
+          <t>524797</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>541140</t>
+          <t>540818</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1067449</t>
+          <t>1066639</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1085895</t>
+          <t>1085407</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57906</t>
+          <t>58559</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94451</t>
+          <t>93367</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>218483</t>
+          <t>215445</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>279133</t>
+          <t>280598</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>287840</t>
+          <t>288860</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>360314</t>
+          <t>361407</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3283167</t>
+          <t>3284251</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3319712</t>
+          <t>3319059</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3252967</t>
+          <t>3251502</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3313617</t>
+          <t>3316655</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6549404</t>
+          <t>6548311</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6621878</t>
+          <t>6620858</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>34333</t>
+          <t>36065</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25614</t>
+          <t>25936</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46955</t>
+          <t>48313</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>98103</t>
+          <t>108325</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85499</t>
+          <t>93653</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>112940</t>
+          <t>123840</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>132436</t>
+          <t>144391</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>116605</t>
+          <t>124448</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>151063</t>
+          <t>163185</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>479119</t>
+          <t>540982</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>466497</t>
+          <t>528734</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>487838</t>
+          <t>551111</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>653629</t>
+          <t>711460</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>638792</t>
+          <t>695945</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>666233</t>
+          <t>726132</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1132747</t>
+          <t>1252441</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1114120</t>
+          <t>1233647</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1148578</t>
+          <t>1272384</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>91,09%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513452</t>
+          <t>577047</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513452</t>
+          <t>577047</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513452</t>
+          <t>577047</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>751732</t>
+          <t>819785</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>751732</t>
+          <t>819785</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>751732</t>
+          <t>819785</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1265183</t>
+          <t>1396832</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1265183</t>
+          <t>1396832</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1265183</t>
+          <t>1396832</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63192</t>
+          <t>71085</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43075</t>
+          <t>56325</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83020</t>
+          <t>89777</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>138356</t>
+          <t>149330</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>100360</t>
+          <t>131299</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>166108</t>
+          <t>172022</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>201548</t>
+          <t>220415</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>160003</t>
+          <t>195094</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>234707</t>
+          <t>248060</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2227135</t>
+          <t>2159481</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2207307</t>
+          <t>2140789</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2247252</t>
+          <t>2174241</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2098789</t>
+          <t>2021377</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2071037</t>
+          <t>1998685</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2136785</t>
+          <t>2039408</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4325924</t>
+          <t>4180859</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4292765</t>
+          <t>4153214</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4367469</t>
+          <t>4206180</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,102 +6223,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14232</t>
+          <t>14604</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7923</t>
+          <t>8297</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24174</t>
+          <t>24398</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>27933</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>19437</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>38321</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>5,21%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>42537</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>31816</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>55733</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>2,2%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>25148</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>18220</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>35232</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>5,33%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>39379</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>28641</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>51680</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -6336,102 +6336,102 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>632391</t>
+          <t>696983</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>622449</t>
+          <t>687189</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>638700</t>
+          <t>703290</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>97,95%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,57%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,83%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>965</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>706944</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>696556</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>715440</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>96,2%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>94,79%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>97,36%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1631</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1403927</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1390731</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1414648</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>97,06%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>96,15%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>97,8%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,26%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>965</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>635315</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>625231</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>642243</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,19%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,67%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>97,24%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1631</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1267707</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1255406</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1278445</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>96,99%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>96,05%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>111757</t>
+          <t>121754</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84603</t>
+          <t>101296</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>135418</t>
+          <t>145347</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>261606</t>
+          <t>285588</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>212173</t>
+          <t>259389</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>292825</t>
+          <t>313804</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>373363</t>
+          <t>407343</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>323657</t>
+          <t>372853</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>412193</t>
+          <t>442950</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3338645</t>
+          <t>3397446</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3314984</t>
+          <t>3373853</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3365799</t>
+          <t>3417904</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3387733</t>
+          <t>3439781</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3356514</t>
+          <t>3411565</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3437166</t>
+          <t>3465980</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6726379</t>
+          <t>6837227</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6687549</t>
+          <t>6801620</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6776085</t>
+          <t>6871717</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450402</t>
+          <t>3519200</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450402</t>
+          <t>3519200</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450402</t>
+          <t>3519200</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3649339</t>
+          <t>3725369</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3649339</t>
+          <t>3725369</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3649339</t>
+          <t>3725369</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7099742</t>
+          <t>7244570</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7099742</t>
+          <t>7244570</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7099742</t>
+          <t>7244570</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
